--- a/equipes_pab.xlsx
+++ b/equipes_pab.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcio Filho\Desktop\sigabases\sigabases-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEECAFCA-4274-42F0-8922-75B984A34A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C250F6-A220-4716-A968-CD2BF3C5DE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="equipes" sheetId="1" r:id="rId1"/>
+    <sheet name="equipe" sheetId="1" r:id="rId1"/>
     <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">equipes!$A$1:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">equipe!$A$1:$E$70</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1080,7 +1080,7 @@
       <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
